--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middellaag.xlsx
@@ -400,22 +400,22 @@
         <v>1.809441918582434</v>
       </c>
       <c r="C2">
-        <v>1.773799324762277</v>
+        <v>1.804986504150216</v>
       </c>
       <c r="D2">
         <v>6.212147121844101</v>
       </c>
       <c r="E2">
-        <v>1.700078601593717</v>
+        <v>1.693446711233219</v>
       </c>
       <c r="F2">
         <v>1.807629892617899</v>
       </c>
       <c r="G2">
-        <v>2.002151662949332</v>
+        <v>1.89978048597444</v>
       </c>
       <c r="H2">
-        <v>1.700317937929736</v>
+        <v>1.693735203374959</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>1.820836472639406</v>
       </c>
       <c r="C3">
-        <v>1.790830877570517</v>
+        <v>1.777853943110417</v>
       </c>
       <c r="D3">
         <v>4.809282045285274</v>
       </c>
       <c r="E3">
-        <v>1.703624045046674</v>
+        <v>1.696783916929245</v>
       </c>
       <c r="F3">
         <v>1.817304492547183</v>
       </c>
       <c r="G3">
-        <v>1.971045113597998</v>
+        <v>1.849965429311619</v>
       </c>
       <c r="H3">
-        <v>1.703193982803088</v>
+        <v>1.696449200345058</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>1.782668010042132</v>
       </c>
       <c r="C4">
-        <v>1.860444782376233</v>
+        <v>1.774452778225331</v>
       </c>
       <c r="D4">
         <v>5.544570533031406</v>
       </c>
       <c r="E4">
-        <v>1.689118343792704</v>
+        <v>1.682414734277926</v>
       </c>
       <c r="F4">
         <v>1.782010133492831</v>
       </c>
       <c r="G4">
-        <v>1.993043150492128</v>
+        <v>1.854084167162709</v>
       </c>
       <c r="H4">
-        <v>1.689607354824598</v>
+        <v>1.682962049416409</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>1.817028306682257</v>
       </c>
       <c r="C5">
-        <v>1.998626836058858</v>
+        <v>1.846433052957773</v>
       </c>
       <c r="D5">
         <v>2.934576195968682</v>
       </c>
       <c r="E5">
-        <v>1.705623931229837</v>
+        <v>1.698637703165205</v>
       </c>
       <c r="F5">
         <v>1.812988199412726</v>
       </c>
       <c r="G5">
-        <v>2.020387323550141</v>
+        <v>1.876641087897798</v>
       </c>
       <c r="H5">
-        <v>1.705018684914926</v>
+        <v>1.698139667833802</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>1.823976775771101</v>
       </c>
       <c r="C6">
-        <v>1.996492174193517</v>
+        <v>1.916531515436447</v>
       </c>
       <c r="D6">
         <v>0.8753565019908747</v>
       </c>
       <c r="E6">
-        <v>1.709811521561945</v>
+        <v>1.702778181237995</v>
       </c>
       <c r="F6">
         <v>1.819960065524299</v>
       </c>
       <c r="G6">
-        <v>1.875463510908506</v>
+        <v>1.857956759342698</v>
       </c>
       <c r="H6">
-        <v>1.709059898859096</v>
+        <v>1.702134782103341</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>1.804522491512453</v>
       </c>
       <c r="C7">
-        <v>2.082638963899223</v>
+        <v>1.879362401327957</v>
       </c>
       <c r="D7">
         <v>1.219932049956221</v>
       </c>
       <c r="E7">
-        <v>1.705657750267797</v>
+        <v>1.698693551260726</v>
       </c>
       <c r="F7">
         <v>1.800608292030371</v>
       </c>
       <c r="G7">
-        <v>1.961212458634178</v>
+        <v>1.834978711092352</v>
       </c>
       <c r="H7">
-        <v>1.705004603960501</v>
+        <v>1.698146787641202</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>1.815118152670408</v>
       </c>
       <c r="C8">
-        <v>1.331268593591207</v>
+        <v>1.683221729337924</v>
       </c>
       <c r="D8">
         <v>1.962454242750494</v>
       </c>
       <c r="E8">
-        <v>1.691569675101092</v>
+        <v>1.685498628784307</v>
       </c>
       <c r="F8">
         <v>1.811121680113447</v>
       </c>
       <c r="G8">
-        <v>1.497617726625957</v>
+        <v>1.767272091689032</v>
       </c>
       <c r="H8">
-        <v>1.691113062267858</v>
+        <v>1.685144340797455</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>1.820110013471357</v>
       </c>
       <c r="C9">
-        <v>1.862728241502912</v>
+        <v>1.757054191355407</v>
       </c>
       <c r="D9">
         <v>1.489277673447329</v>
       </c>
       <c r="E9">
-        <v>1.699117520271849</v>
+        <v>1.692202314332432</v>
       </c>
       <c r="F9">
         <v>1.816956055849429</v>
       </c>
       <c r="G9">
-        <v>1.812437534362182</v>
+        <v>1.766819276858553</v>
       </c>
       <c r="H9">
-        <v>1.699213878649834</v>
+        <v>1.692402558551635</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>1.575784862706459</v>
       </c>
       <c r="C10">
-        <v>2.084409928598445</v>
+        <v>1.842578070853054</v>
       </c>
       <c r="D10">
         <v>3.05232573247321</v>
       </c>
       <c r="E10">
-        <v>1.664463245616165</v>
+        <v>1.658377414931971</v>
       </c>
       <c r="F10">
         <v>1.584180934600335</v>
       </c>
       <c r="G10">
-        <v>2.033644326230509</v>
+        <v>1.854518068625072</v>
       </c>
       <c r="H10">
-        <v>1.667191889118646</v>
+        <v>1.661081076980147</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -634,22 +634,22 @@
         <v>1.524747233310899</v>
       </c>
       <c r="C11">
-        <v>2.106358068430189</v>
+        <v>1.860091254811437</v>
       </c>
       <c r="D11">
         <v>2.462184757981164</v>
       </c>
       <c r="E11">
-        <v>1.670736457539432</v>
+        <v>1.664602016793604</v>
       </c>
       <c r="F11">
         <v>1.532756793977353</v>
       </c>
       <c r="G11">
-        <v>2.025370691254477</v>
+        <v>1.845563763123255</v>
       </c>
       <c r="H11">
-        <v>1.671843872822301</v>
+        <v>1.665767752176606</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>1.275774180011838</v>
       </c>
       <c r="C12">
-        <v>2.058589535148216</v>
+        <v>1.802448729004363</v>
       </c>
       <c r="D12">
         <v>0.6115296961620866</v>
       </c>
       <c r="E12">
-        <v>1.617529040115271</v>
+        <v>1.611899663964373</v>
       </c>
       <c r="F12">
         <v>1.280968368999796</v>
       </c>
       <c r="G12">
-        <v>1.892787997103477</v>
+        <v>1.720672658826846</v>
       </c>
       <c r="H12">
-        <v>1.617368168486356</v>
+        <v>1.611816605513263</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>1.559307860733567</v>
       </c>
       <c r="C13">
-        <v>2.079739547593902</v>
+        <v>1.833607780622675</v>
       </c>
       <c r="D13">
         <v>2.16724232412129</v>
       </c>
       <c r="E13">
-        <v>1.65828505256153</v>
+        <v>1.651970098391188</v>
       </c>
       <c r="F13">
         <v>1.565073904619898</v>
       </c>
       <c r="G13">
-        <v>1.989697056952975</v>
+        <v>1.814690078601969</v>
       </c>
       <c r="H13">
-        <v>1.659963471116275</v>
+        <v>1.65373929412394</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_middellaag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
